--- a/gestione_coordinate_pois_calcolo.xlsx
+++ b/gestione_coordinate_pois_calcolo.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\Quadrilatero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC82449F-ED84-4A35-9756-9EF31DE29F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D20F65-D878-4EB1-B8CE-656E81820AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="348" yWindow="348" windowWidth="15708" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="1188" windowWidth="15708" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -437,6 +450,7 @@
   <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -474,7 +488,7 @@
         <v>44.49911485308791</v>
       </c>
       <c r="C2">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D2">
         <v>44.49911485308791</v>
@@ -483,10 +497,18 @@
         <v>11.33668386365537</v>
       </c>
       <c r="F2">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G2">
         <v>11.33668386365537</v>
+      </c>
+      <c r="I2">
+        <f>B2+C2</f>
+        <v>44.498914853087911</v>
+      </c>
+      <c r="J2">
+        <f>E2+F2</f>
+        <v>11.33660386365537</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -497,7 +519,7 @@
         <v>44.498944000000002</v>
       </c>
       <c r="C3">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D3">
         <v>44.498944000000002</v>
@@ -506,10 +528,18 @@
         <v>11.340329000000001</v>
       </c>
       <c r="F3">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G3">
         <v>11.340329000000001</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I15" si="0">B3+C3</f>
+        <v>44.498744000000002</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J15" si="1">E3+F3</f>
+        <v>11.340249</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -520,7 +550,7 @@
         <v>44.50018</v>
       </c>
       <c r="C4">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D4">
         <v>44.50018</v>
@@ -529,10 +559,18 @@
         <v>11.33807</v>
       </c>
       <c r="F4">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G4">
         <v>11.33807</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>44.499980000000001</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="1"/>
+        <v>11.33799</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -543,7 +581,7 @@
         <v>44.498063683720687</v>
       </c>
       <c r="C5">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D5">
         <v>44.498063683720687</v>
@@ -552,10 +590,18 @@
         <v>11.341926289317311</v>
       </c>
       <c r="F5">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G5">
         <v>11.341926289317311</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>44.497863683720688</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>11.34184628931731</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -566,7 +612,7 @@
         <v>44.500663888888901</v>
       </c>
       <c r="C6">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D6">
         <v>44.500663888888901</v>
@@ -575,10 +621,18 @@
         <v>11.340769444444399</v>
       </c>
       <c r="F6">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G6">
         <v>11.340769444444399</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>44.500463888888902</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>11.340689444444399</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -589,7 +643,7 @@
         <v>44.50018</v>
       </c>
       <c r="C7">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D7">
         <v>44.499899999999997</v>
@@ -598,10 +652,18 @@
         <v>11.339986</v>
       </c>
       <c r="F7">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G7">
         <v>11.3399</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>44.499980000000001</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>11.339905999999999</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -612,7 +674,7 @@
         <v>44.499997222222198</v>
       </c>
       <c r="C8">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D8">
         <v>44.499997222222198</v>
@@ -621,10 +683,18 @@
         <v>11.340388888888899</v>
       </c>
       <c r="F8">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G8">
         <v>11.340388888888899</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>44.499797222222199</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>11.340308888888899</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -635,7 +705,7 @@
         <v>44.499252779999999</v>
       </c>
       <c r="C9">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D9">
         <v>44.499252779999999</v>
@@ -644,10 +714,18 @@
         <v>11.34074444</v>
       </c>
       <c r="F9">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G9">
         <v>11.34074444</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>44.49905278</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>11.340664439999999</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -658,7 +736,7 @@
         <v>44.501514</v>
       </c>
       <c r="C10">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D10">
         <v>44.501514</v>
@@ -667,10 +745,18 @@
         <v>11.343557000000001</v>
       </c>
       <c r="F10">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G10">
         <v>11.343557000000001</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>44.501314000000001</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>11.343477</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -681,7 +767,7 @@
         <v>44.498899000000002</v>
       </c>
       <c r="C11">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D11">
         <v>44.498899000000002</v>
@@ -690,10 +776,18 @@
         <v>11.342153</v>
       </c>
       <c r="F11">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G11">
         <v>11.342153</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>44.498699000000002</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>11.342072999999999</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -704,7 +798,7 @@
         <v>44.498899000000002</v>
       </c>
       <c r="C12">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D12">
         <v>44.498899000000002</v>
@@ -713,10 +807,18 @@
         <v>11.342241</v>
       </c>
       <c r="F12">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G12">
         <v>11.342241</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>44.498699000000002</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>11.342160999999999</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -727,7 +829,7 @@
         <v>44.499068999999999</v>
       </c>
       <c r="C13">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D13">
         <v>44.499068999999999</v>
@@ -736,10 +838,18 @@
         <v>11.341809</v>
       </c>
       <c r="F13">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G13">
         <v>11.341809</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>44.498868999999999</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>11.341728999999999</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -750,7 +860,7 @@
         <v>44.499079999999999</v>
       </c>
       <c r="C14">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D14">
         <v>44.499079999999999</v>
@@ -759,10 +869,18 @@
         <v>11.342241100000001</v>
       </c>
       <c r="F14">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G14">
         <v>11.342241100000001</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>44.49888</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="1"/>
+        <v>11.3421611</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -773,7 +891,7 @@
         <v>44.501248758211673</v>
       </c>
       <c r="C15">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D15">
         <v>44.501248758211673</v>
@@ -782,10 +900,18 @@
         <v>11.34075366622929</v>
       </c>
       <c r="F15">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G15">
         <v>11.34075366622929</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>44.501048758211674</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>11.340673666229289</v>
       </c>
       <c r="L15" s="1"/>
     </row>
